--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:28:26+00:00</t>
+    <t>2023-12-19T10:34:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:34:37+00:00</t>
+    <t>2024-01-06T18:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-06T18:57:36+00:00</t>
+    <t>2024-01-08T22:02:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:06+00:00</t>
+    <t>2024-01-08T22:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:40+00:00</t>
+    <t>2024-03-19T10:43:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-19T10:43:29+00:00</t>
+    <t>2024-04-03T07:46:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1267,7 +1267,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|RelatedPerson)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -2600,7 +2600,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="218.36328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:46:18+00:00</t>
+    <t>2024-04-03T10:16:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1267,7 +1267,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|RelatedPerson)
 </t>
   </si>
   <si>
@@ -2600,7 +2600,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="218.36328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T10:16:02+00:00</t>
+    <t>2024-04-10T06:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Denmark (http://www.hl7.dk, jenskristianvilladsen@gmail.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -1267,7 +1267,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|RelatedPerson)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -2600,7 +2600,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="218.36328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T06:34:41+00:00</t>
+    <t>2024-04-11T09:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-11T09:53:59+00:00</t>
+    <t>2024-04-12T06:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T06:23:14+00:00</t>
+    <t>2024-04-16T10:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-16T10:58:26+00:00</t>
+    <t>2024-04-18T15:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:20:26+00:00</t>
+    <t>2024-04-18T15:27:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:27:51+00:00</t>
+    <t>2024-04-22T11:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T11:01:11+00:00</t>
+    <t>2024-04-22T12:03:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T12:03:36+00:00</t>
+    <t>2024-04-22T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T13:38:01+00:00</t>
+    <t>2024-04-23T08:24:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T08:24:27+00:00</t>
+    <t>2024-04-23T10:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T10:50:14+00:00</t>
+    <t>2024-04-23T18:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T18:15:55+00:00</t>
+    <t>2024-05-02T12:47:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-02T12:47:39+00:00</t>
+    <t>2024-05-03T13:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T13:03:24+00:00</t>
+    <t>2024-05-06T06:35:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T06:35:09+00:00</t>
+    <t>2024-05-06T07:49:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T07:49:19+00:00</t>
+    <t>2024-05-06T14:14:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T14:14:33+00:00</t>
+    <t>2024-05-10T08:40:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7050" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7050" uniqueCount="735">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T08:40:47+00:00</t>
+    <t>2024-05-10T19:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1682,6 +1682,9 @@
   </si>
   <si>
     <t>Observation.method.coding.system</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct|http://snomed.info/sct/554471000005108</t>
   </si>
   <si>
     <t>Observation.method.coding:SCTCode.version</t>
@@ -14023,7 +14026,7 @@
         <v>82</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>298</v>
+        <v>539</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>82</v>
@@ -14097,10 +14100,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14217,10 +14220,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14337,10 +14340,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14457,10 +14460,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14579,10 +14582,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14701,10 +14704,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14727,16 +14730,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14786,7 +14789,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14804,27 +14807,27 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14847,16 +14850,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14906,7 +14909,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14924,27 +14927,27 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14967,19 +14970,19 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -15028,7 +15031,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15040,7 +15043,7 @@
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>82</v>
@@ -15049,10 +15052,10 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -15063,10 +15066,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15181,10 +15184,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15301,14 +15304,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -15330,10 +15333,10 @@
         <v>139</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>142</v>
@@ -15388,7 +15391,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15423,10 +15426,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15449,13 +15452,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15506,7 +15509,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15515,7 +15518,7 @@
         <v>93</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>105</v>
@@ -15527,10 +15530,10 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15541,10 +15544,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15567,13 +15570,13 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15624,7 +15627,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15633,7 +15636,7 @@
         <v>93</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>105</v>
@@ -15645,10 +15648,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15659,10 +15662,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15688,16 +15691,16 @@
         <v>191</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15725,10 +15728,10 @@
         <v>117</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -15746,7 +15749,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15764,10 +15767,10 @@
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>498</v>
@@ -15781,10 +15784,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15810,16 +15813,16 @@
         <v>191</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15847,10 +15850,10 @@
         <v>207</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
@@ -15868,7 +15871,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15886,10 +15889,10 @@
         <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>498</v>
@@ -15903,10 +15906,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15929,17 +15932,17 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15988,7 +15991,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16012,7 +16015,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -16023,10 +16026,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16052,10 +16055,10 @@
         <v>217</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16106,7 +16109,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16127,10 +16130,10 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16141,10 +16144,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16167,16 +16170,16 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16226,7 +16229,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16247,10 +16250,10 @@
         <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -16261,10 +16264,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16287,16 +16290,16 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16346,7 +16349,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16367,10 +16370,10 @@
         <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16381,10 +16384,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16407,19 +16410,19 @@
         <v>94</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16468,7 +16471,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16489,10 +16492,10 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16503,10 +16506,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16621,10 +16624,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16741,14 +16744,14 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16770,10 +16773,10 @@
         <v>139</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>142</v>
@@ -16828,7 +16831,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16863,10 +16866,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16892,13 +16895,13 @@
         <v>191</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="O119" t="s" s="2">
         <v>206</v>
@@ -16950,7 +16953,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>93</v>
@@ -16968,7 +16971,7 @@
         <v>82</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>212</v>
@@ -16985,10 +16988,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17103,10 +17106,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17223,10 +17226,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17343,10 +17346,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="B123" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>239</v>
@@ -17467,10 +17470,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17585,10 +17588,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17705,10 +17708,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17827,10 +17830,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17947,10 +17950,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18067,10 +18070,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18187,10 +18190,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18309,10 +18312,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C131" t="s" s="2">
         <v>292</v>
@@ -18433,10 +18436,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18551,10 +18554,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18671,10 +18674,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18793,10 +18796,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18913,10 +18916,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19033,10 +19036,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19153,10 +19156,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19275,10 +19278,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C139" t="s" s="2">
         <v>304</v>
@@ -19399,10 +19402,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19517,10 +19520,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19637,10 +19640,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19759,10 +19762,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19879,10 +19882,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19999,10 +20002,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20119,10 +20122,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20241,10 +20244,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C147" t="s" s="2">
         <v>316</v>
@@ -20365,10 +20368,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20483,10 +20486,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20603,10 +20606,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20725,10 +20728,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20845,10 +20848,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20965,10 +20968,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21085,10 +21088,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21207,10 +21210,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C155" t="s" s="2">
         <v>328</v>
@@ -21331,10 +21334,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21449,10 +21452,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21569,10 +21572,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21691,10 +21694,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21811,10 +21814,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21931,10 +21934,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22051,10 +22054,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22173,10 +22176,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>339</v>
@@ -22204,7 +22207,7 @@
         <v>229</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M163" t="s" s="2">
         <v>231</v>
@@ -22297,10 +22300,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22415,10 +22418,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22535,10 +22538,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22657,10 +22660,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22777,10 +22780,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22897,10 +22900,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23017,10 +23020,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23139,10 +23142,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23261,10 +23264,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23290,13 +23293,13 @@
         <v>413</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M172" t="s" s="2">
         <v>415</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="O172" t="s" s="2">
         <v>417</v>
@@ -23346,7 +23349,7 @@
         <v>419</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23364,7 +23367,7 @@
         <v>82</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>422</v>
@@ -23381,10 +23384,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C173" t="s" s="2">
         <v>426</v>
@@ -23412,13 +23415,13 @@
         <v>427</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M173" t="s" s="2">
         <v>415</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="O173" t="s" s="2">
         <v>417</v>
@@ -23470,7 +23473,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23488,7 +23491,7 @@
         <v>82</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>422</v>
@@ -23505,10 +23508,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23623,10 +23626,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23743,10 +23746,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23865,10 +23868,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23987,10 +23990,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24107,10 +24110,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24225,10 +24228,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24347,10 +24350,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24376,13 +24379,13 @@
         <v>191</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="O181" t="s" s="2">
         <v>483</v>
@@ -24434,7 +24437,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -24469,10 +24472,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24556,7 +24559,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24591,10 +24594,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24620,16 +24623,16 @@
         <v>83</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -24678,7 +24681,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24699,10 +24702,10 @@
         <v>82</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T19:12:38+00:00</t>
+    <t>2024-05-12T08:40:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1122,7 +1122,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|Location|Device)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|http://hl7.dk/fhir/core/StructureDefinition/dk-core-location|Device)
 </t>
   </si>
   <si>
@@ -1267,7 +1267,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:40:34+00:00</t>
+    <t>2024-05-12T08:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$183</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:41:58+00:00</t>
+    <t>2024-05-12T09:45:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -279,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}dk-core-observation-mandatory-units:If value is specified then unit and/or code must be specified {value.ofType(Quantity).value.exists() implies value.ofType(Quantity).unit.exists() or value.ofType(Quantity).code.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}ipa-obs-1:If there is no component or hasMember element then either a value[x] or a data absent reason must be present {(component.empty() and hasMember.empty()) implies (dataAbsentReason or value)}dk-core-observation-mandatory-units:If value is specified then unit and/or code must be specified {value.ofType(Quantity).value.exists() implies value.ofType(Quantity).unit.exists() or value.ofType(Quantity).code.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1122,7 +1125,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|http://hl7.dk/fhir/core/StructureDefinition/dk-core-location|Device)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient)
 </t>
   </si>
   <si>
@@ -1267,7 +1270,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|Organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -1318,8 +1321,8 @@
     <t>closed</t>
   </si>
   <si>
-    <t xml:space="preserve">obs-7
-</t>
+    <t>obs-7
+ipa-obs-1</t>
   </si>
   <si>
     <t>&lt; 441742003 |Evaluation finding|</t>
@@ -1521,8 +1524,8 @@
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
-    <t xml:space="preserve">obs-6
-</t>
+    <t>obs-6
+ipa-obs-1</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -1682,9 +1685,6 @@
   </si>
   <si>
     <t>Observation.method.coding.system</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct|http://snomed.info/sct/554471000005108</t>
   </si>
   <si>
     <t>Observation.method.coding:SCTCode.version</t>
@@ -1955,7 +1955,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -2277,6 +2277,10 @@
   <si>
     <t>"Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obs-6
+</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>
@@ -2417,6 +2421,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -2603,7 +2622,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="218.88671875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2764,7 +2783,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2884,7 +2903,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>92</v>
       </c>
@@ -3004,7 +3023,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>100</v>
       </c>
@@ -3122,7 +3141,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>106</v>
       </c>
@@ -3242,7 +3261,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>112</v>
       </c>
@@ -3362,7 +3381,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>121</v>
       </c>
@@ -3482,7 +3501,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>129</v>
       </c>
@@ -3602,7 +3621,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>137</v>
       </c>
@@ -3722,7 +3741,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>145</v>
       </c>
@@ -3844,7 +3863,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>150</v>
       </c>
@@ -3964,7 +3983,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>159</v>
       </c>
@@ -4084,7 +4103,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>168</v>
       </c>
@@ -4204,7 +4223,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>177</v>
       </c>
@@ -4223,7 +4242,7 @@
         <v>93</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>94</v>
@@ -4326,7 +4345,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>190</v>
       </c>
@@ -4345,7 +4364,7 @@
         <v>93</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>82</v>
@@ -4448,7 +4467,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>201</v>
       </c>
@@ -4467,7 +4486,7 @@
         <v>93</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>82</v>
@@ -4570,7 +4589,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>216</v>
       </c>
@@ -4688,7 +4707,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>222</v>
       </c>
@@ -4808,7 +4827,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>228</v>
       </c>
@@ -4928,7 +4947,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>238</v>
       </c>
@@ -5050,7 +5069,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>243</v>
       </c>
@@ -5168,7 +5187,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>245</v>
       </c>
@@ -5288,7 +5307,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>247</v>
       </c>
@@ -5410,7 +5429,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>257</v>
       </c>
@@ -5530,7 +5549,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>265</v>
       </c>
@@ -5650,7 +5669,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>273</v>
       </c>
@@ -5770,7 +5789,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>281</v>
       </c>
@@ -5892,7 +5911,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>291</v>
       </c>
@@ -6014,7 +6033,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>295</v>
       </c>
@@ -6132,7 +6151,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>296</v>
       </c>
@@ -6252,7 +6271,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>297</v>
       </c>
@@ -6374,7 +6393,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>299</v>
       </c>
@@ -6494,7 +6513,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>300</v>
       </c>
@@ -6614,7 +6633,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>301</v>
       </c>
@@ -6734,7 +6753,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>302</v>
       </c>
@@ -6856,7 +6875,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>303</v>
       </c>
@@ -6978,7 +6997,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>307</v>
       </c>
@@ -7096,7 +7115,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>308</v>
       </c>
@@ -7216,7 +7235,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>309</v>
       </c>
@@ -7338,7 +7357,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>311</v>
       </c>
@@ -7458,7 +7477,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>312</v>
       </c>
@@ -7578,7 +7597,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>313</v>
       </c>
@@ -7698,7 +7717,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>314</v>
       </c>
@@ -7820,7 +7839,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>315</v>
       </c>
@@ -7942,7 +7961,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>319</v>
       </c>
@@ -8060,7 +8079,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>320</v>
       </c>
@@ -8180,7 +8199,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>321</v>
       </c>
@@ -8302,7 +8321,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>323</v>
       </c>
@@ -8422,7 +8441,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>324</v>
       </c>
@@ -8542,7 +8561,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>325</v>
       </c>
@@ -8662,7 +8681,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>326</v>
       </c>
@@ -8784,7 +8803,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>327</v>
       </c>
@@ -8908,7 +8927,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>330</v>
       </c>
@@ -9026,7 +9045,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>331</v>
       </c>
@@ -9146,7 +9165,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>332</v>
       </c>
@@ -9268,7 +9287,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>334</v>
       </c>
@@ -9388,7 +9407,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>335</v>
       </c>
@@ -9508,7 +9527,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>336</v>
       </c>
@@ -9628,7 +9647,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>337</v>
       </c>
@@ -9750,7 +9769,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>338</v>
       </c>
@@ -9874,7 +9893,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>341</v>
       </c>
@@ -9992,7 +10011,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>342</v>
       </c>
@@ -10112,7 +10131,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>343</v>
       </c>
@@ -10234,7 +10253,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>345</v>
       </c>
@@ -10354,7 +10373,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>346</v>
       </c>
@@ -10474,7 +10493,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>347</v>
       </c>
@@ -10594,7 +10613,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
         <v>348</v>
       </c>
@@ -10716,7 +10735,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
         <v>349</v>
       </c>
@@ -10838,7 +10857,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>357</v>
       </c>
@@ -10857,7 +10876,7 @@
         <v>93</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>82</v>
@@ -10960,7 +10979,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
         <v>367</v>
       </c>
@@ -11080,7 +11099,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
         <v>373</v>
       </c>
@@ -11202,7 +11221,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
         <v>384</v>
       </c>
@@ -11221,7 +11240,7 @@
         <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>82</v>
@@ -11324,7 +11343,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
         <v>395</v>
       </c>
@@ -11444,7 +11463,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
         <v>403</v>
       </c>
@@ -11564,7 +11583,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
         <v>412</v>
       </c>
@@ -11583,7 +11602,7 @@
         <v>93</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>82</v>
@@ -11684,7 +11703,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
         <v>425</v>
       </c>
@@ -11705,7 +11724,7 @@
         <v>93</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>82</v>
@@ -11808,7 +11827,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
         <v>428</v>
       </c>
@@ -11926,7 +11945,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
         <v>430</v>
       </c>
@@ -12046,7 +12065,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
         <v>432</v>
       </c>
@@ -12168,7 +12187,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
         <v>442</v>
       </c>
@@ -12290,7 +12309,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
         <v>453</v>
       </c>
@@ -12410,7 +12429,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
         <v>461</v>
       </c>
@@ -12528,7 +12547,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
         <v>471</v>
       </c>
@@ -12650,7 +12669,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
         <v>479</v>
       </c>
@@ -12669,7 +12688,7 @@
         <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>82</v>
@@ -12772,7 +12791,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
         <v>488</v>
       </c>
@@ -12894,7 +12913,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
         <v>500</v>
       </c>
@@ -13016,7 +13035,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
         <v>508</v>
       </c>
@@ -13136,7 +13155,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
         <v>518</v>
       </c>
@@ -13258,7 +13277,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
         <v>527</v>
       </c>
@@ -13376,7 +13395,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
         <v>528</v>
       </c>
@@ -13496,7 +13515,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
         <v>529</v>
       </c>
@@ -13616,7 +13635,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
         <v>530</v>
       </c>
@@ -13738,7 +13757,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
         <v>533</v>
       </c>
@@ -13856,7 +13875,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
         <v>535</v>
       </c>
@@ -13976,7 +13995,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
         <v>537</v>
       </c>
@@ -14026,7 +14045,7 @@
         <v>82</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>539</v>
+        <v>298</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>82</v>
@@ -14098,12 +14117,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14218,12 +14237,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14338,12 +14357,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14458,12 +14477,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14580,12 +14599,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14702,12 +14721,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14730,16 +14749,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14789,7 +14808,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14807,27 +14826,27 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AM101" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="AM101" t="s" s="2">
+      <c r="AN101" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="AN101" t="s" s="2">
+      <c r="AO101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP101" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="AO101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP101" t="s" s="2">
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
         <v>557</v>
       </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s" s="2">
-        <v>558</v>
-      </c>
       <c r="B102" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14850,16 +14869,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14909,7 +14928,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14927,27 +14946,27 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AM102" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="AM102" t="s" s="2">
+      <c r="AN102" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="AN102" t="s" s="2">
+      <c r="AO102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP102" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="AO102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP102" t="s" s="2">
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
         <v>566</v>
       </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s" s="2">
-        <v>567</v>
-      </c>
       <c r="B103" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14970,19 +14989,19 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -15031,7 +15050,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15043,33 +15062,33 @@
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM103" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="AK103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM103" t="s" s="2">
+      <c r="AN103" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="AN103" t="s" s="2">
+      <c r="AO103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="AO103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s" s="2">
-        <v>576</v>
-      </c>
       <c r="B104" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15182,12 +15201,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15302,16 +15321,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -15333,10 +15352,10 @@
         <v>139</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>142</v>
@@ -15391,7 +15410,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15424,12 +15443,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15452,13 +15471,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15509,7 +15528,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15518,7 +15537,7 @@
         <v>93</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>105</v>
@@ -15530,24 +15549,24 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="AN107" t="s" s="2">
+      <c r="AO107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP107" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="AO107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s" s="2">
-        <v>590</v>
-      </c>
       <c r="B108" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15570,13 +15589,13 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15627,7 +15646,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15636,7 +15655,7 @@
         <v>93</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>105</v>
@@ -15648,24 +15667,24 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AN108" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="AO108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP108" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s" s="2">
-        <v>594</v>
-      </c>
       <c r="B109" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15691,16 +15710,16 @@
         <v>191</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="N109" t="s" s="2">
+      <c r="O109" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15728,11 +15747,11 @@
         <v>117</v>
       </c>
       <c r="Y109" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="Z109" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="Z109" t="s" s="2">
-        <v>600</v>
-      </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15749,7 +15768,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15767,10 +15786,10 @@
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AM109" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>498</v>
@@ -15782,12 +15801,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15813,16 +15832,16 @@
         <v>191</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="N110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15850,11 +15869,11 @@
         <v>207</v>
       </c>
       <c r="Y110" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="Z110" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="Z110" t="s" s="2">
-        <v>609</v>
-      </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
       </c>
@@ -15871,7 +15890,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15889,10 +15908,10 @@
         <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AM110" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>498</v>
@@ -15904,12 +15923,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15932,17 +15951,17 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15991,7 +16010,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16015,21 +16034,21 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP111" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="AO111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP111" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s" s="2">
-        <v>616</v>
-      </c>
       <c r="B112" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16055,10 +16074,10 @@
         <v>217</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16109,7 +16128,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16130,24 +16149,24 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AN112" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP112" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="AO112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP112" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s" s="2">
-        <v>620</v>
-      </c>
       <c r="B113" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16170,16 +16189,16 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16229,7 +16248,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16250,24 +16269,24 @@
         <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AN113" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="AN113" t="s" s="2">
+      <c r="AO113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP113" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="AO113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP113" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s" s="2">
-        <v>627</v>
-      </c>
       <c r="B114" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16290,16 +16309,16 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L114" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="M114" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16349,7 +16368,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16370,24 +16389,24 @@
         <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AN114" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP114" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="AO114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP114" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s" s="2">
-        <v>633</v>
-      </c>
       <c r="B115" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16410,19 +16429,19 @@
         <v>94</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="N115" t="s" s="2">
+      <c r="O115" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16471,7 +16490,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16492,24 +16511,24 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AN115" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="AN115" t="s" s="2">
+      <c r="AO115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP115" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="AO115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP115" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s" s="2">
-        <v>640</v>
-      </c>
       <c r="B116" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16622,12 +16641,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16742,16 +16761,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16773,10 +16792,10 @@
         <v>139</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>142</v>
@@ -16831,7 +16850,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16864,12 +16883,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16895,13 +16914,13 @@
         <v>191</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="O119" t="s" s="2">
         <v>206</v>
@@ -16953,7 +16972,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>93</v>
@@ -16971,7 +16990,7 @@
         <v>82</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>212</v>
@@ -16986,12 +17005,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17104,12 +17123,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17224,12 +17243,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17344,12 +17363,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>239</v>
@@ -17468,12 +17487,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="B124" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17586,12 +17605,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="B125" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17706,12 +17725,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="B126" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17828,12 +17847,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="B127" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17948,12 +17967,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="B128" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18068,12 +18087,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="B129" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18188,12 +18207,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="B130" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18310,12 +18329,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C131" t="s" s="2">
         <v>292</v>
@@ -18434,12 +18453,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18552,12 +18571,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18672,12 +18691,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18794,12 +18813,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18914,12 +18933,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19034,12 +19053,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19154,12 +19173,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19276,12 +19295,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C139" t="s" s="2">
         <v>304</v>
@@ -19400,12 +19419,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19518,12 +19537,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19638,12 +19657,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19760,12 +19779,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19880,12 +19899,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20000,12 +20019,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20120,12 +20139,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20242,12 +20261,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C147" t="s" s="2">
         <v>316</v>
@@ -20366,12 +20385,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20484,12 +20503,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20604,12 +20623,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20726,12 +20745,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20846,12 +20865,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20966,12 +20985,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21086,12 +21105,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21208,12 +21227,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C155" t="s" s="2">
         <v>328</v>
@@ -21332,12 +21351,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21450,12 +21469,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21570,12 +21589,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21692,12 +21711,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21812,12 +21831,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21932,12 +21951,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22052,12 +22071,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22174,12 +22193,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>339</v>
@@ -22207,7 +22226,7 @@
         <v>229</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="M163" t="s" s="2">
         <v>231</v>
@@ -22298,12 +22317,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22416,12 +22435,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22536,12 +22555,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22658,12 +22677,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22778,12 +22797,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22898,12 +22917,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23018,12 +23037,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23140,12 +23159,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23262,12 +23281,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23293,13 +23312,13 @@
         <v>413</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="M172" t="s" s="2">
         <v>415</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="O172" t="s" s="2">
         <v>417</v>
@@ -23349,7 +23368,7 @@
         <v>419</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23367,7 +23386,7 @@
         <v>82</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>422</v>
@@ -23382,12 +23401,12 @@
         <v>424</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C173" t="s" s="2">
         <v>426</v>
@@ -23415,13 +23434,13 @@
         <v>427</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="M173" t="s" s="2">
         <v>415</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="O173" t="s" s="2">
         <v>417</v>
@@ -23473,7 +23492,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23491,7 +23510,7 @@
         <v>82</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>422</v>
@@ -23506,12 +23525,12 @@
         <v>424</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="B174" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="B174" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23624,12 +23643,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="B175" t="s" s="2">
         <v>715</v>
-      </c>
-      <c r="B175" t="s" s="2">
-        <v>716</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23744,12 +23763,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="B176" t="s" s="2">
         <v>717</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>718</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23866,12 +23885,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="B177" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23988,12 +24007,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="B178" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="B178" t="s" s="2">
-        <v>722</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24108,12 +24127,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="B179" t="s" s="2">
         <v>723</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>724</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24226,12 +24245,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="B180" t="s" s="2">
         <v>725</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>726</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24348,12 +24367,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24379,13 +24398,13 @@
         <v>191</v>
       </c>
       <c r="L181" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="M181" t="s" s="2">
         <v>728</v>
       </c>
-      <c r="M181" t="s" s="2">
+      <c r="N181" t="s" s="2">
         <v>729</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>730</v>
       </c>
       <c r="O181" t="s" s="2">
         <v>483</v>
@@ -24437,7 +24456,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -24446,7 +24465,7 @@
         <v>93</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>486</v>
+        <v>730</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>105</v>
@@ -24470,7 +24489,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
         <v>731</v>
       </c>
@@ -24592,7 +24611,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
         <v>732</v>
       </c>
@@ -24629,10 +24648,10 @@
         <v>734</v>
       </c>
       <c r="N183" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="O183" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="O183" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -24702,10 +24721,10 @@
         <v>82</v>
       </c>
       <c r="AM183" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AN183" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="AN183" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>82</v>
@@ -24715,6 +24734,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AP183">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI182">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T09:45:49+00:00</t>
+    <t>2024-05-12T11:37:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$183</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7050" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7050" uniqueCount="734">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T11:37:02+00:00</t>
+    <t>2024-06-03T20:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -282,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}ipa-obs-1:If there is no component or hasMember element then either a value[x] or a data absent reason must be present {(component.empty() and hasMember.empty()) implies (dataAbsentReason or value)}dk-core-observation-mandatory-units:If value is specified then unit and/or code must be specified {value.ofType(Quantity).value.exists() implies value.ofType(Quantity).unit.exists() or value.ofType(Quantity).code.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}dk-core-observation-mandatory-units:If value is specified then unit and/or code must be specified {value.ofType(Quantity).value.exists() implies value.ofType(Quantity).unit.exists() or value.ofType(Quantity).code.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1125,7 +1122,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|Location|Device)
 </t>
   </si>
   <si>
@@ -1321,8 +1318,8 @@
     <t>closed</t>
   </si>
   <si>
-    <t>obs-7
-ipa-obs-1</t>
+    <t xml:space="preserve">obs-7
+</t>
   </si>
   <si>
     <t>&lt; 441742003 |Evaluation finding|</t>
@@ -1524,8 +1521,8 @@
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
-    <t>obs-6
-ipa-obs-1</t>
+    <t xml:space="preserve">obs-6
+</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -1955,7 +1952,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -2277,10 +2274,6 @@
   <si>
     <t>"Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obs-6
-</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>
@@ -2421,21 +2414,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -2783,7 +2761,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2903,7 +2881,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>92</v>
       </c>
@@ -3023,7 +3001,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>100</v>
       </c>
@@ -3141,7 +3119,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>106</v>
       </c>
@@ -3261,7 +3239,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>112</v>
       </c>
@@ -3381,7 +3359,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>121</v>
       </c>
@@ -3501,7 +3479,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>129</v>
       </c>
@@ -3621,7 +3599,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>137</v>
       </c>
@@ -3741,7 +3719,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>145</v>
       </c>
@@ -3863,7 +3841,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>150</v>
       </c>
@@ -3983,7 +3961,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>159</v>
       </c>
@@ -4103,7 +4081,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>168</v>
       </c>
@@ -4223,7 +4201,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>177</v>
       </c>
@@ -4242,7 +4220,7 @@
         <v>93</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>94</v>
@@ -4345,7 +4323,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>190</v>
       </c>
@@ -4364,7 +4342,7 @@
         <v>93</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>82</v>
@@ -4467,7 +4445,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>201</v>
       </c>
@@ -4486,7 +4464,7 @@
         <v>93</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>82</v>
@@ -4589,7 +4567,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>216</v>
       </c>
@@ -4707,7 +4685,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>222</v>
       </c>
@@ -4827,7 +4805,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>228</v>
       </c>
@@ -4947,7 +4925,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>238</v>
       </c>
@@ -5069,7 +5047,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>243</v>
       </c>
@@ -5187,7 +5165,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>245</v>
       </c>
@@ -5307,7 +5285,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>247</v>
       </c>
@@ -5429,7 +5407,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>257</v>
       </c>
@@ -5549,7 +5527,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>265</v>
       </c>
@@ -5669,7 +5647,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>273</v>
       </c>
@@ -5789,7 +5767,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>281</v>
       </c>
@@ -5911,7 +5889,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>291</v>
       </c>
@@ -6033,7 +6011,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>295</v>
       </c>
@@ -6151,7 +6129,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>296</v>
       </c>
@@ -6271,7 +6249,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>297</v>
       </c>
@@ -6393,7 +6371,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>299</v>
       </c>
@@ -6513,7 +6491,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>300</v>
       </c>
@@ -6633,7 +6611,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>301</v>
       </c>
@@ -6753,7 +6731,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>302</v>
       </c>
@@ -6875,7 +6853,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>303</v>
       </c>
@@ -6997,7 +6975,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>307</v>
       </c>
@@ -7115,7 +7093,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>308</v>
       </c>
@@ -7235,7 +7213,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>309</v>
       </c>
@@ -7357,7 +7335,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>311</v>
       </c>
@@ -7477,7 +7455,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>312</v>
       </c>
@@ -7597,7 +7575,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>313</v>
       </c>
@@ -7717,7 +7695,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>314</v>
       </c>
@@ -7839,7 +7817,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>315</v>
       </c>
@@ -7961,7 +7939,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>319</v>
       </c>
@@ -8079,7 +8057,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>320</v>
       </c>
@@ -8199,7 +8177,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>321</v>
       </c>
@@ -8321,7 +8299,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>323</v>
       </c>
@@ -8441,7 +8419,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>324</v>
       </c>
@@ -8561,7 +8539,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>325</v>
       </c>
@@ -8681,7 +8659,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>326</v>
       </c>
@@ -8803,7 +8781,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>327</v>
       </c>
@@ -8927,7 +8905,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>330</v>
       </c>
@@ -9045,7 +9023,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>331</v>
       </c>
@@ -9165,7 +9143,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>332</v>
       </c>
@@ -9287,7 +9265,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>334</v>
       </c>
@@ -9407,7 +9385,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
         <v>335</v>
       </c>
@@ -9527,7 +9505,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>336</v>
       </c>
@@ -9647,7 +9625,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
         <v>337</v>
       </c>
@@ -9769,7 +9747,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>338</v>
       </c>
@@ -9893,7 +9871,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>341</v>
       </c>
@@ -10011,7 +9989,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>342</v>
       </c>
@@ -10131,7 +10109,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>343</v>
       </c>
@@ -10253,7 +10231,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>345</v>
       </c>
@@ -10373,7 +10351,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>346</v>
       </c>
@@ -10493,7 +10471,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>347</v>
       </c>
@@ -10613,7 +10591,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>348</v>
       </c>
@@ -10735,7 +10713,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>349</v>
       </c>
@@ -10857,7 +10835,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
         <v>357</v>
       </c>
@@ -10876,7 +10854,7 @@
         <v>93</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>82</v>
@@ -10979,7 +10957,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>367</v>
       </c>
@@ -11099,7 +11077,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
         <v>373</v>
       </c>
@@ -11221,7 +11199,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
         <v>384</v>
       </c>
@@ -11240,7 +11218,7 @@
         <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>82</v>
@@ -11343,7 +11321,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
         <v>395</v>
       </c>
@@ -11463,7 +11441,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
         <v>403</v>
       </c>
@@ -11583,7 +11561,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
         <v>412</v>
       </c>
@@ -11602,7 +11580,7 @@
         <v>93</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>82</v>
@@ -11703,7 +11681,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
         <v>425</v>
       </c>
@@ -11724,7 +11702,7 @@
         <v>93</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>82</v>
@@ -11827,7 +11805,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
         <v>428</v>
       </c>
@@ -11945,7 +11923,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
         <v>430</v>
       </c>
@@ -12065,7 +12043,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
         <v>432</v>
       </c>
@@ -12187,7 +12165,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
         <v>442</v>
       </c>
@@ -12309,7 +12287,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>453</v>
       </c>
@@ -12429,7 +12407,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
         <v>461</v>
       </c>
@@ -12547,7 +12525,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
         <v>471</v>
       </c>
@@ -12669,7 +12647,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
         <v>479</v>
       </c>
@@ -12688,7 +12666,7 @@
         <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>82</v>
@@ -12791,7 +12769,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
         <v>488</v>
       </c>
@@ -12913,7 +12891,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
         <v>500</v>
       </c>
@@ -13035,7 +13013,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
         <v>508</v>
       </c>
@@ -13155,7 +13133,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
         <v>518</v>
       </c>
@@ -13277,7 +13255,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
         <v>527</v>
       </c>
@@ -13395,7 +13373,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
         <v>528</v>
       </c>
@@ -13515,7 +13493,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
         <v>529</v>
       </c>
@@ -13635,7 +13613,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
         <v>530</v>
       </c>
@@ -13757,7 +13735,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
         <v>533</v>
       </c>
@@ -13875,7 +13853,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
         <v>535</v>
       </c>
@@ -13995,7 +13973,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
         <v>537</v>
       </c>
@@ -14117,7 +14095,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
         <v>539</v>
       </c>
@@ -14237,7 +14215,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
         <v>541</v>
       </c>
@@ -14357,7 +14335,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
         <v>543</v>
       </c>
@@ -14477,7 +14455,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
         <v>545</v>
       </c>
@@ -14599,7 +14577,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
         <v>547</v>
       </c>
@@ -14721,7 +14699,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
         <v>548</v>
       </c>
@@ -14841,7 +14819,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="102" hidden="true">
+    <row r="102">
       <c r="A102" t="s" s="2">
         <v>557</v>
       </c>
@@ -14961,7 +14939,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
         <v>566</v>
       </c>
@@ -15083,7 +15061,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
         <v>575</v>
       </c>
@@ -15201,7 +15179,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="105" hidden="true">
+    <row r="105">
       <c r="A105" t="s" s="2">
         <v>576</v>
       </c>
@@ -15321,7 +15299,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="106" hidden="true">
+    <row r="106">
       <c r="A106" t="s" s="2">
         <v>577</v>
       </c>
@@ -15443,7 +15421,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="107" hidden="true">
+    <row r="107">
       <c r="A107" t="s" s="2">
         <v>582</v>
       </c>
@@ -15561,7 +15539,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
         <v>589</v>
       </c>
@@ -15679,7 +15657,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
         <v>593</v>
       </c>
@@ -15801,7 +15779,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="110" hidden="true">
+    <row r="110">
       <c r="A110" t="s" s="2">
         <v>602</v>
       </c>
@@ -15923,7 +15901,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="111" hidden="true">
+    <row r="111">
       <c r="A111" t="s" s="2">
         <v>609</v>
       </c>
@@ -16043,7 +16021,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="112" hidden="true">
+    <row r="112">
       <c r="A112" t="s" s="2">
         <v>615</v>
       </c>
@@ -16161,7 +16139,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
         <v>619</v>
       </c>
@@ -16281,7 +16259,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="114" hidden="true">
+    <row r="114">
       <c r="A114" t="s" s="2">
         <v>626</v>
       </c>
@@ -16401,7 +16379,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
         <v>632</v>
       </c>
@@ -16523,7 +16501,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="116" hidden="true">
+    <row r="116">
       <c r="A116" t="s" s="2">
         <v>639</v>
       </c>
@@ -16641,7 +16619,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="117" hidden="true">
+    <row r="117">
       <c r="A117" t="s" s="2">
         <v>640</v>
       </c>
@@ -16761,7 +16739,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="118" hidden="true">
+    <row r="118">
       <c r="A118" t="s" s="2">
         <v>641</v>
       </c>
@@ -16883,7 +16861,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="119" hidden="true">
+    <row r="119">
       <c r="A119" t="s" s="2">
         <v>642</v>
       </c>
@@ -17005,7 +16983,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="120" hidden="true">
+    <row r="120">
       <c r="A120" t="s" s="2">
         <v>647</v>
       </c>
@@ -17123,7 +17101,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="121" hidden="true">
+    <row r="121">
       <c r="A121" t="s" s="2">
         <v>648</v>
       </c>
@@ -17243,7 +17221,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="122" hidden="true">
+    <row r="122">
       <c r="A122" t="s" s="2">
         <v>649</v>
       </c>
@@ -17363,7 +17341,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="123" hidden="true">
+    <row r="123">
       <c r="A123" t="s" s="2">
         <v>650</v>
       </c>
@@ -17487,7 +17465,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="124" hidden="true">
+    <row r="124">
       <c r="A124" t="s" s="2">
         <v>651</v>
       </c>
@@ -17605,7 +17583,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="125" hidden="true">
+    <row r="125">
       <c r="A125" t="s" s="2">
         <v>653</v>
       </c>
@@ -17725,7 +17703,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="126" hidden="true">
+    <row r="126">
       <c r="A126" t="s" s="2">
         <v>655</v>
       </c>
@@ -17847,7 +17825,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="127" hidden="true">
+    <row r="127">
       <c r="A127" t="s" s="2">
         <v>657</v>
       </c>
@@ -17967,7 +17945,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="128" hidden="true">
+    <row r="128">
       <c r="A128" t="s" s="2">
         <v>659</v>
       </c>
@@ -18087,7 +18065,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="129" hidden="true">
+    <row r="129">
       <c r="A129" t="s" s="2">
         <v>661</v>
       </c>
@@ -18207,7 +18185,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="130" hidden="true">
+    <row r="130">
       <c r="A130" t="s" s="2">
         <v>663</v>
       </c>
@@ -18329,7 +18307,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="131" hidden="true">
+    <row r="131">
       <c r="A131" t="s" s="2">
         <v>665</v>
       </c>
@@ -18453,7 +18431,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="132" hidden="true">
+    <row r="132">
       <c r="A132" t="s" s="2">
         <v>666</v>
       </c>
@@ -18571,7 +18549,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="133" hidden="true">
+    <row r="133">
       <c r="A133" t="s" s="2">
         <v>667</v>
       </c>
@@ -18691,7 +18669,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="134" hidden="true">
+    <row r="134">
       <c r="A134" t="s" s="2">
         <v>668</v>
       </c>
@@ -18813,7 +18791,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="135" hidden="true">
+    <row r="135">
       <c r="A135" t="s" s="2">
         <v>669</v>
       </c>
@@ -18933,7 +18911,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="136" hidden="true">
+    <row r="136">
       <c r="A136" t="s" s="2">
         <v>670</v>
       </c>
@@ -19053,7 +19031,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="137" hidden="true">
+    <row r="137">
       <c r="A137" t="s" s="2">
         <v>671</v>
       </c>
@@ -19173,7 +19151,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="138" hidden="true">
+    <row r="138">
       <c r="A138" t="s" s="2">
         <v>672</v>
       </c>
@@ -19295,7 +19273,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="139" hidden="true">
+    <row r="139">
       <c r="A139" t="s" s="2">
         <v>673</v>
       </c>
@@ -19419,7 +19397,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="140" hidden="true">
+    <row r="140">
       <c r="A140" t="s" s="2">
         <v>674</v>
       </c>
@@ -19537,7 +19515,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="141" hidden="true">
+    <row r="141">
       <c r="A141" t="s" s="2">
         <v>675</v>
       </c>
@@ -19657,7 +19635,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="142" hidden="true">
+    <row r="142">
       <c r="A142" t="s" s="2">
         <v>676</v>
       </c>
@@ -19779,7 +19757,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="143" hidden="true">
+    <row r="143">
       <c r="A143" t="s" s="2">
         <v>677</v>
       </c>
@@ -19899,7 +19877,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="144" hidden="true">
+    <row r="144">
       <c r="A144" t="s" s="2">
         <v>678</v>
       </c>
@@ -20019,7 +19997,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="145" hidden="true">
+    <row r="145">
       <c r="A145" t="s" s="2">
         <v>679</v>
       </c>
@@ -20139,7 +20117,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="146" hidden="true">
+    <row r="146">
       <c r="A146" t="s" s="2">
         <v>680</v>
       </c>
@@ -20261,7 +20239,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="147" hidden="true">
+    <row r="147">
       <c r="A147" t="s" s="2">
         <v>681</v>
       </c>
@@ -20385,7 +20363,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="148" hidden="true">
+    <row r="148">
       <c r="A148" t="s" s="2">
         <v>682</v>
       </c>
@@ -20503,7 +20481,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="149" hidden="true">
+    <row r="149">
       <c r="A149" t="s" s="2">
         <v>683</v>
       </c>
@@ -20623,7 +20601,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="150" hidden="true">
+    <row r="150">
       <c r="A150" t="s" s="2">
         <v>684</v>
       </c>
@@ -20745,7 +20723,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="151" hidden="true">
+    <row r="151">
       <c r="A151" t="s" s="2">
         <v>685</v>
       </c>
@@ -20865,7 +20843,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="152" hidden="true">
+    <row r="152">
       <c r="A152" t="s" s="2">
         <v>686</v>
       </c>
@@ -20985,7 +20963,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="153" hidden="true">
+    <row r="153">
       <c r="A153" t="s" s="2">
         <v>687</v>
       </c>
@@ -21105,7 +21083,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="154" hidden="true">
+    <row r="154">
       <c r="A154" t="s" s="2">
         <v>688</v>
       </c>
@@ -21227,7 +21205,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="155" hidden="true">
+    <row r="155">
       <c r="A155" t="s" s="2">
         <v>689</v>
       </c>
@@ -21351,7 +21329,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="156" hidden="true">
+    <row r="156">
       <c r="A156" t="s" s="2">
         <v>690</v>
       </c>
@@ -21469,7 +21447,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="157" hidden="true">
+    <row r="157">
       <c r="A157" t="s" s="2">
         <v>691</v>
       </c>
@@ -21589,7 +21567,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="158" hidden="true">
+    <row r="158">
       <c r="A158" t="s" s="2">
         <v>692</v>
       </c>
@@ -21711,7 +21689,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="159" hidden="true">
+    <row r="159">
       <c r="A159" t="s" s="2">
         <v>693</v>
       </c>
@@ -21831,7 +21809,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="160" hidden="true">
+    <row r="160">
       <c r="A160" t="s" s="2">
         <v>694</v>
       </c>
@@ -21951,7 +21929,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="161" hidden="true">
+    <row r="161">
       <c r="A161" t="s" s="2">
         <v>695</v>
       </c>
@@ -22071,7 +22049,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="162" hidden="true">
+    <row r="162">
       <c r="A162" t="s" s="2">
         <v>696</v>
       </c>
@@ -22193,7 +22171,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="163" hidden="true">
+    <row r="163">
       <c r="A163" t="s" s="2">
         <v>697</v>
       </c>
@@ -22317,7 +22295,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="164" hidden="true">
+    <row r="164">
       <c r="A164" t="s" s="2">
         <v>699</v>
       </c>
@@ -22435,7 +22413,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="165" hidden="true">
+    <row r="165">
       <c r="A165" t="s" s="2">
         <v>700</v>
       </c>
@@ -22555,7 +22533,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="166" hidden="true">
+    <row r="166">
       <c r="A166" t="s" s="2">
         <v>701</v>
       </c>
@@ -22677,7 +22655,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="167" hidden="true">
+    <row r="167">
       <c r="A167" t="s" s="2">
         <v>702</v>
       </c>
@@ -22797,7 +22775,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="168" hidden="true">
+    <row r="168">
       <c r="A168" t="s" s="2">
         <v>703</v>
       </c>
@@ -22917,7 +22895,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="169" hidden="true">
+    <row r="169">
       <c r="A169" t="s" s="2">
         <v>704</v>
       </c>
@@ -23037,7 +23015,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="170" hidden="true">
+    <row r="170">
       <c r="A170" t="s" s="2">
         <v>705</v>
       </c>
@@ -23159,7 +23137,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="171" hidden="true">
+    <row r="171">
       <c r="A171" t="s" s="2">
         <v>706</v>
       </c>
@@ -23281,7 +23259,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="172" hidden="true">
+    <row r="172">
       <c r="A172" t="s" s="2">
         <v>707</v>
       </c>
@@ -23401,7 +23379,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="173" hidden="true">
+    <row r="173">
       <c r="A173" t="s" s="2">
         <v>711</v>
       </c>
@@ -23525,7 +23503,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="174" hidden="true">
+    <row r="174">
       <c r="A174" t="s" s="2">
         <v>712</v>
       </c>
@@ -23643,7 +23621,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="175" hidden="true">
+    <row r="175">
       <c r="A175" t="s" s="2">
         <v>714</v>
       </c>
@@ -23763,7 +23741,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="176" hidden="true">
+    <row r="176">
       <c r="A176" t="s" s="2">
         <v>716</v>
       </c>
@@ -23885,7 +23863,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="177" hidden="true">
+    <row r="177">
       <c r="A177" t="s" s="2">
         <v>718</v>
       </c>
@@ -24007,7 +23985,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="178" hidden="true">
+    <row r="178">
       <c r="A178" t="s" s="2">
         <v>720</v>
       </c>
@@ -24127,7 +24105,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="179" hidden="true">
+    <row r="179">
       <c r="A179" t="s" s="2">
         <v>722</v>
       </c>
@@ -24245,7 +24223,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="180" hidden="true">
+    <row r="180">
       <c r="A180" t="s" s="2">
         <v>724</v>
       </c>
@@ -24367,7 +24345,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="181" hidden="true">
+    <row r="181">
       <c r="A181" t="s" s="2">
         <v>726</v>
       </c>
@@ -24465,7 +24443,7 @@
         <v>93</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>730</v>
+        <v>486</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>105</v>
@@ -24489,12 +24467,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="182" hidden="true">
+    <row r="182">
       <c r="A182" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24578,7 +24556,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24611,12 +24589,12 @@
         <v>499</v>
       </c>
     </row>
-    <row r="183" hidden="true">
+    <row r="183">
       <c r="A183" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24642,10 +24620,10 @@
         <v>83</v>
       </c>
       <c r="L183" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="M183" t="s" s="2">
         <v>733</v>
-      </c>
-      <c r="M183" t="s" s="2">
-        <v>734</v>
       </c>
       <c r="N183" t="s" s="2">
         <v>570</v>
@@ -24700,7 +24678,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24734,24 +24712,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP183">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI182">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7050" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7050" uniqueCount="735">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T20:51:53+00:00</t>
+    <t>2024-06-25T21:12:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1122,7 +1122,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|Location|Device)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|http://hl7.dk/fhir/core/StructureDefinition/dk-core-location|Device)
 </t>
   </si>
   <si>
@@ -1267,7 +1267,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|Organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -1682,6 +1682,9 @@
   </si>
   <si>
     <t>Observation.method.coding.system</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct|http://snomed.info/sct/554471000005108</t>
   </si>
   <si>
     <t>Observation.method.coding:SCTCode.version</t>
@@ -2600,7 +2603,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="218.88671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -14023,7 +14026,7 @@
         <v>82</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>298</v>
+        <v>539</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>82</v>
@@ -14097,10 +14100,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14217,10 +14220,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14337,10 +14340,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14457,10 +14460,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14579,10 +14582,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14701,10 +14704,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14727,16 +14730,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14786,7 +14789,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14804,27 +14807,27 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14847,16 +14850,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14906,7 +14909,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14924,27 +14927,27 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14967,19 +14970,19 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -15028,7 +15031,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15040,7 +15043,7 @@
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>82</v>
@@ -15049,10 +15052,10 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -15063,10 +15066,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15181,10 +15184,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15301,14 +15304,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -15330,10 +15333,10 @@
         <v>139</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>142</v>
@@ -15388,7 +15391,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15423,10 +15426,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15449,13 +15452,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15506,7 +15509,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15515,7 +15518,7 @@
         <v>93</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>105</v>
@@ -15527,10 +15530,10 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15541,10 +15544,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15567,13 +15570,13 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15624,7 +15627,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15633,7 +15636,7 @@
         <v>93</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>105</v>
@@ -15645,10 +15648,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15659,10 +15662,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15688,16 +15691,16 @@
         <v>191</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15725,10 +15728,10 @@
         <v>117</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -15746,7 +15749,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15764,10 +15767,10 @@
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>498</v>
@@ -15781,10 +15784,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15810,16 +15813,16 @@
         <v>191</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15847,10 +15850,10 @@
         <v>207</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
@@ -15868,7 +15871,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15886,10 +15889,10 @@
         <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>498</v>
@@ -15903,10 +15906,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15929,17 +15932,17 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15988,7 +15991,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16012,7 +16015,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -16023,10 +16026,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16052,10 +16055,10 @@
         <v>217</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16106,7 +16109,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16127,10 +16130,10 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16141,10 +16144,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16167,16 +16170,16 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16226,7 +16229,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16247,10 +16250,10 @@
         <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -16261,10 +16264,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16287,16 +16290,16 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16346,7 +16349,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16367,10 +16370,10 @@
         <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16381,10 +16384,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16407,19 +16410,19 @@
         <v>94</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16468,7 +16471,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16489,10 +16492,10 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16503,10 +16506,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16621,10 +16624,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16741,14 +16744,14 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16770,10 +16773,10 @@
         <v>139</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>142</v>
@@ -16828,7 +16831,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16863,10 +16866,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16892,13 +16895,13 @@
         <v>191</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="O119" t="s" s="2">
         <v>206</v>
@@ -16950,7 +16953,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>93</v>
@@ -16968,7 +16971,7 @@
         <v>82</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>212</v>
@@ -16985,10 +16988,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17103,10 +17106,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17223,10 +17226,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17343,10 +17346,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="B123" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>239</v>
@@ -17467,10 +17470,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17585,10 +17588,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17705,10 +17708,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17827,10 +17830,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17947,10 +17950,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18067,10 +18070,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18187,10 +18190,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18309,10 +18312,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C131" t="s" s="2">
         <v>292</v>
@@ -18433,10 +18436,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18551,10 +18554,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18671,10 +18674,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18793,10 +18796,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18913,10 +18916,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19033,10 +19036,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19153,10 +19156,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19275,10 +19278,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C139" t="s" s="2">
         <v>304</v>
@@ -19399,10 +19402,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19517,10 +19520,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19637,10 +19640,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19759,10 +19762,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19879,10 +19882,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19999,10 +20002,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20119,10 +20122,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20241,10 +20244,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C147" t="s" s="2">
         <v>316</v>
@@ -20365,10 +20368,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20483,10 +20486,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20603,10 +20606,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20725,10 +20728,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20845,10 +20848,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20965,10 +20968,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21085,10 +21088,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21207,10 +21210,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C155" t="s" s="2">
         <v>328</v>
@@ -21331,10 +21334,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21449,10 +21452,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21569,10 +21572,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21691,10 +21694,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21811,10 +21814,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21931,10 +21934,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22051,10 +22054,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22173,10 +22176,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>339</v>
@@ -22204,7 +22207,7 @@
         <v>229</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M163" t="s" s="2">
         <v>231</v>
@@ -22297,10 +22300,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22415,10 +22418,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22535,10 +22538,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22657,10 +22660,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22777,10 +22780,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22897,10 +22900,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23017,10 +23020,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23139,10 +23142,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23261,10 +23264,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23290,13 +23293,13 @@
         <v>413</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M172" t="s" s="2">
         <v>415</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="O172" t="s" s="2">
         <v>417</v>
@@ -23346,7 +23349,7 @@
         <v>419</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23364,7 +23367,7 @@
         <v>82</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>422</v>
@@ -23381,10 +23384,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C173" t="s" s="2">
         <v>426</v>
@@ -23412,13 +23415,13 @@
         <v>427</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M173" t="s" s="2">
         <v>415</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="O173" t="s" s="2">
         <v>417</v>
@@ -23470,7 +23473,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23488,7 +23491,7 @@
         <v>82</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>422</v>
@@ -23505,10 +23508,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23623,10 +23626,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23743,10 +23746,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23865,10 +23868,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23987,10 +23990,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24107,10 +24110,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24225,10 +24228,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24347,10 +24350,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24376,13 +24379,13 @@
         <v>191</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="O181" t="s" s="2">
         <v>483</v>
@@ -24434,7 +24437,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -24469,10 +24472,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24556,7 +24559,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24591,10 +24594,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24620,16 +24623,16 @@
         <v>83</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -24678,7 +24681,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24699,10 +24702,10 @@
         <v>82</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:12:53+00:00</t>
+    <t>2024-06-25T21:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:21:07+00:00</t>
+    <t>2024-06-25T21:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:20:43+00:00</t>
+    <t>2024-06-25T21:42:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:42:34+00:00</t>
+    <t>2024-06-26T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-26T14:36:19+00:00</t>
+    <t>2024-06-27T10:47:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-27T10:47:07+00:00</t>
+    <t>2024-08-11T15:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-11T15:57:41+00:00</t>
+    <t>2024-10-17T12:12:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1955,7 +1955,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7050" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7050" uniqueCount="734">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:12:58+00:00</t>
+    <t>2024-10-17T12:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1122,7 +1122,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|http://hl7.dk/fhir/core/StructureDefinition/dk-core-location|Device)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|Location|Device)
 </t>
   </si>
   <si>
@@ -1267,7 +1267,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -1682,9 +1682,6 @@
   </si>
   <si>
     <t>Observation.method.coding.system</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct|http://snomed.info/sct/554471000005108</t>
   </si>
   <si>
     <t>Observation.method.coding:SCTCode.version</t>
@@ -14026,7 +14023,7 @@
         <v>82</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>539</v>
+        <v>298</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>82</v>
@@ -14100,10 +14097,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14220,10 +14217,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14340,10 +14337,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14460,10 +14457,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14582,10 +14579,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14704,10 +14701,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14730,16 +14727,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14789,7 +14786,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14807,27 +14804,27 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AM101" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="AM101" t="s" s="2">
+      <c r="AN101" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="AN101" t="s" s="2">
+      <c r="AO101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP101" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>557</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14850,16 +14847,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14909,7 +14906,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14927,27 +14924,27 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AM102" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="AM102" t="s" s="2">
+      <c r="AN102" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="AN102" t="s" s="2">
+      <c r="AO102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP102" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>566</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14970,19 +14967,19 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -15031,7 +15028,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15043,19 +15040,19 @@
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM103" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="AK103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM103" t="s" s="2">
+      <c r="AN103" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -15066,10 +15063,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15184,10 +15181,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15304,14 +15301,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -15333,10 +15330,10 @@
         <v>139</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>142</v>
@@ -15391,7 +15388,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15426,10 +15423,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15452,13 +15449,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15509,7 +15506,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15518,7 +15515,7 @@
         <v>93</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>105</v>
@@ -15530,10 +15527,10 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15544,10 +15541,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15570,13 +15567,13 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15627,7 +15624,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15636,7 +15633,7 @@
         <v>93</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>105</v>
@@ -15648,10 +15645,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15662,10 +15659,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15691,16 +15688,16 @@
         <v>191</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="N109" t="s" s="2">
+      <c r="O109" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15728,11 +15725,11 @@
         <v>117</v>
       </c>
       <c r="Y109" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="Z109" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="Z109" t="s" s="2">
-        <v>600</v>
-      </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15749,7 +15746,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15767,10 +15764,10 @@
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AM109" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>498</v>
@@ -15784,10 +15781,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15813,16 +15810,16 @@
         <v>191</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="N110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15850,11 +15847,11 @@
         <v>207</v>
       </c>
       <c r="Y110" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="Z110" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="Z110" t="s" s="2">
-        <v>609</v>
-      </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
       </c>
@@ -15871,7 +15868,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15889,10 +15886,10 @@
         <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AM110" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>498</v>
@@ -15906,10 +15903,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15932,17 +15929,17 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15991,7 +15988,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16015,7 +16012,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -16026,10 +16023,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16055,10 +16052,10 @@
         <v>217</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16109,7 +16106,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16130,10 +16127,10 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16144,10 +16141,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16170,16 +16167,16 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16229,7 +16226,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16250,10 +16247,10 @@
         <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AN113" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -16264,10 +16261,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16290,16 +16287,16 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L114" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="M114" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16349,7 +16346,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16370,10 +16367,10 @@
         <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16384,10 +16381,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16410,19 +16407,19 @@
         <v>94</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="N115" t="s" s="2">
+      <c r="O115" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16471,7 +16468,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16492,10 +16489,10 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AN115" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16506,10 +16503,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16624,10 +16621,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16744,14 +16741,14 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16773,10 +16770,10 @@
         <v>139</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>142</v>
@@ -16831,7 +16828,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16866,10 +16863,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16895,13 +16892,13 @@
         <v>191</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="O119" t="s" s="2">
         <v>206</v>
@@ -16953,7 +16950,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>93</v>
@@ -16971,7 +16968,7 @@
         <v>82</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>212</v>
@@ -16988,10 +16985,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17106,10 +17103,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17226,10 +17223,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17346,10 +17343,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>239</v>
@@ -17470,10 +17467,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="B124" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17588,10 +17585,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="B125" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17708,10 +17705,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="B126" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17830,10 +17827,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="B127" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17950,10 +17947,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="B128" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18070,10 +18067,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="B129" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18190,10 +18187,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="B130" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18312,10 +18309,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C131" t="s" s="2">
         <v>292</v>
@@ -18436,10 +18433,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18554,10 +18551,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18674,10 +18671,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18796,10 +18793,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18916,10 +18913,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19036,10 +19033,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19156,10 +19153,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19278,10 +19275,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C139" t="s" s="2">
         <v>304</v>
@@ -19402,10 +19399,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19520,10 +19517,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19640,10 +19637,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19762,10 +19759,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19882,10 +19879,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20002,10 +19999,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20122,10 +20119,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20244,10 +20241,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C147" t="s" s="2">
         <v>316</v>
@@ -20368,10 +20365,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20486,10 +20483,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20606,10 +20603,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20728,10 +20725,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20848,10 +20845,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20968,10 +20965,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21088,10 +21085,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21210,10 +21207,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C155" t="s" s="2">
         <v>328</v>
@@ -21334,10 +21331,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21452,10 +21449,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21572,10 +21569,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21694,10 +21691,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21814,10 +21811,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21934,10 +21931,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22054,10 +22051,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22176,10 +22173,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>339</v>
@@ -22207,7 +22204,7 @@
         <v>229</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="M163" t="s" s="2">
         <v>231</v>
@@ -22300,10 +22297,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22418,10 +22415,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22538,10 +22535,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22660,10 +22657,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22780,10 +22777,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22900,10 +22897,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23020,10 +23017,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23142,10 +23139,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23264,10 +23261,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23293,13 +23290,13 @@
         <v>413</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="M172" t="s" s="2">
         <v>415</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="O172" t="s" s="2">
         <v>417</v>
@@ -23349,7 +23346,7 @@
         <v>419</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23367,7 +23364,7 @@
         <v>82</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>422</v>
@@ -23384,10 +23381,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C173" t="s" s="2">
         <v>426</v>
@@ -23415,13 +23412,13 @@
         <v>427</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="M173" t="s" s="2">
         <v>415</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="O173" t="s" s="2">
         <v>417</v>
@@ -23473,7 +23470,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23491,7 +23488,7 @@
         <v>82</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>422</v>
@@ -23508,10 +23505,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="B174" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="B174" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23626,10 +23623,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="B175" t="s" s="2">
         <v>715</v>
-      </c>
-      <c r="B175" t="s" s="2">
-        <v>716</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23746,10 +23743,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="B176" t="s" s="2">
         <v>717</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>718</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23868,10 +23865,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="B177" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23990,10 +23987,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="B178" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="B178" t="s" s="2">
-        <v>722</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24110,10 +24107,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="B179" t="s" s="2">
         <v>723</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>724</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24228,10 +24225,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="B180" t="s" s="2">
         <v>725</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>726</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24350,10 +24347,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24379,13 +24376,13 @@
         <v>191</v>
       </c>
       <c r="L181" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="M181" t="s" s="2">
         <v>728</v>
       </c>
-      <c r="M181" t="s" s="2">
+      <c r="N181" t="s" s="2">
         <v>729</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>730</v>
       </c>
       <c r="O181" t="s" s="2">
         <v>483</v>
@@ -24437,7 +24434,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -24472,10 +24469,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24559,7 +24556,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24594,10 +24591,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24623,16 +24620,16 @@
         <v>83</v>
       </c>
       <c r="L183" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="M183" t="s" s="2">
         <v>733</v>
       </c>
-      <c r="M183" t="s" s="2">
-        <v>734</v>
-      </c>
       <c r="N183" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="O183" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="O183" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -24681,7 +24678,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24702,10 +24699,10 @@
         <v>82</v>
       </c>
       <c r="AM183" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AN183" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="AN183" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7050" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7050" uniqueCount="735">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:15:17+00:00</t>
+    <t>2024-10-18T06:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1122,7 +1122,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|Location|Device)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|http://hl7.dk/fhir/core/StructureDefinition/dk-core-location|Device)
 </t>
   </si>
   <si>
@@ -1267,7 +1267,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -1682,6 +1682,9 @@
   </si>
   <si>
     <t>Observation.method.coding.system</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct|http://snomed.info/sct/554471000005108</t>
   </si>
   <si>
     <t>Observation.method.coding:SCTCode.version</t>
@@ -14023,7 +14026,7 @@
         <v>82</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>298</v>
+        <v>539</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>82</v>
@@ -14097,10 +14100,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14217,10 +14220,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14337,10 +14340,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14457,10 +14460,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14579,10 +14582,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14701,10 +14704,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14727,16 +14730,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14786,7 +14789,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14804,27 +14807,27 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14847,16 +14850,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14906,7 +14909,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14924,27 +14927,27 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14967,19 +14970,19 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -15028,7 +15031,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15040,7 +15043,7 @@
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>82</v>
@@ -15049,10 +15052,10 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -15063,10 +15066,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15181,10 +15184,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15301,14 +15304,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -15330,10 +15333,10 @@
         <v>139</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>142</v>
@@ -15388,7 +15391,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15423,10 +15426,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15449,13 +15452,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15506,7 +15509,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15515,7 +15518,7 @@
         <v>93</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>105</v>
@@ -15527,10 +15530,10 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15541,10 +15544,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15567,13 +15570,13 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15624,7 +15627,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15633,7 +15636,7 @@
         <v>93</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>105</v>
@@ -15645,10 +15648,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15659,10 +15662,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15688,16 +15691,16 @@
         <v>191</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15725,10 +15728,10 @@
         <v>117</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -15746,7 +15749,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15764,10 +15767,10 @@
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>498</v>
@@ -15781,10 +15784,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15810,16 +15813,16 @@
         <v>191</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15847,10 +15850,10 @@
         <v>207</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
@@ -15868,7 +15871,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15886,10 +15889,10 @@
         <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>498</v>
@@ -15903,10 +15906,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15929,17 +15932,17 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15988,7 +15991,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16012,7 +16015,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -16023,10 +16026,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16052,10 +16055,10 @@
         <v>217</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16106,7 +16109,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16127,10 +16130,10 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16141,10 +16144,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16167,16 +16170,16 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16226,7 +16229,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16247,10 +16250,10 @@
         <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -16261,10 +16264,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16287,16 +16290,16 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16346,7 +16349,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16367,10 +16370,10 @@
         <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16381,10 +16384,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16407,19 +16410,19 @@
         <v>94</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16468,7 +16471,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16489,10 +16492,10 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16503,10 +16506,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16621,10 +16624,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16741,14 +16744,14 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16770,10 +16773,10 @@
         <v>139</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>142</v>
@@ -16828,7 +16831,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16863,10 +16866,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16892,13 +16895,13 @@
         <v>191</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="O119" t="s" s="2">
         <v>206</v>
@@ -16950,7 +16953,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>93</v>
@@ -16968,7 +16971,7 @@
         <v>82</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>212</v>
@@ -16985,10 +16988,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17103,10 +17106,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17223,10 +17226,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17343,10 +17346,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="B123" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>239</v>
@@ -17467,10 +17470,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17585,10 +17588,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17705,10 +17708,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17827,10 +17830,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17947,10 +17950,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18067,10 +18070,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18187,10 +18190,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18309,10 +18312,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C131" t="s" s="2">
         <v>292</v>
@@ -18433,10 +18436,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18551,10 +18554,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18671,10 +18674,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18793,10 +18796,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18913,10 +18916,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19033,10 +19036,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19153,10 +19156,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19275,10 +19278,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C139" t="s" s="2">
         <v>304</v>
@@ -19399,10 +19402,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19517,10 +19520,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19637,10 +19640,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19759,10 +19762,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19879,10 +19882,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19999,10 +20002,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20119,10 +20122,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20241,10 +20244,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C147" t="s" s="2">
         <v>316</v>
@@ -20365,10 +20368,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20483,10 +20486,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20603,10 +20606,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20725,10 +20728,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20845,10 +20848,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20965,10 +20968,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21085,10 +21088,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21207,10 +21210,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C155" t="s" s="2">
         <v>328</v>
@@ -21331,10 +21334,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21449,10 +21452,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21569,10 +21572,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21691,10 +21694,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21811,10 +21814,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21931,10 +21934,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22051,10 +22054,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22173,10 +22176,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>339</v>
@@ -22204,7 +22207,7 @@
         <v>229</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M163" t="s" s="2">
         <v>231</v>
@@ -22297,10 +22300,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22415,10 +22418,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22535,10 +22538,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22657,10 +22660,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22777,10 +22780,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22897,10 +22900,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23017,10 +23020,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23139,10 +23142,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23261,10 +23264,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23290,13 +23293,13 @@
         <v>413</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M172" t="s" s="2">
         <v>415</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="O172" t="s" s="2">
         <v>417</v>
@@ -23346,7 +23349,7 @@
         <v>419</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23364,7 +23367,7 @@
         <v>82</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>422</v>
@@ -23381,10 +23384,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C173" t="s" s="2">
         <v>426</v>
@@ -23412,13 +23415,13 @@
         <v>427</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M173" t="s" s="2">
         <v>415</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="O173" t="s" s="2">
         <v>417</v>
@@ -23470,7 +23473,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23488,7 +23491,7 @@
         <v>82</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>422</v>
@@ -23505,10 +23508,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23623,10 +23626,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23743,10 +23746,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23865,10 +23868,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23987,10 +23990,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24107,10 +24110,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24225,10 +24228,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24347,10 +24350,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24376,13 +24379,13 @@
         <v>191</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="O181" t="s" s="2">
         <v>483</v>
@@ -24434,7 +24437,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -24469,10 +24472,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24556,7 +24559,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24591,10 +24594,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24620,16 +24623,16 @@
         <v>83</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -24678,7 +24681,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24699,10 +24702,10 @@
         <v>82</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T06:07:37+00:00</t>
+    <t>2024-10-27T12:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T12:31:37+00:00</t>
+    <t>2024-11-04T14:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:15:57+00:00</t>
+    <t>2024-11-04T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:58:42+00:00</t>
+    <t>2024-11-04T15:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T15:07:28+00:00</t>
+    <t>2024-11-05T12:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7050" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7050" uniqueCount="734">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.4.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T12:45:46+00:00</t>
+    <t>2024-11-15T12:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1122,7 +1122,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|http://hl7.dk/fhir/core/StructureDefinition/dk-core-location|Device)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|Location|Device)
 </t>
   </si>
   <si>
@@ -1267,7 +1267,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -1682,9 +1682,6 @@
   </si>
   <si>
     <t>Observation.method.coding.system</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct|http://snomed.info/sct/554471000005108</t>
   </si>
   <si>
     <t>Observation.method.coding:SCTCode.version</t>
@@ -14026,7 +14023,7 @@
         <v>82</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>539</v>
+        <v>298</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>82</v>
@@ -14100,10 +14097,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14220,10 +14217,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14340,10 +14337,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14460,10 +14457,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14582,10 +14579,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14704,10 +14701,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14730,16 +14727,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14789,7 +14786,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14807,27 +14804,27 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AM101" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="AM101" t="s" s="2">
+      <c r="AN101" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="AN101" t="s" s="2">
+      <c r="AO101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP101" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>557</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14850,16 +14847,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14909,7 +14906,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14927,27 +14924,27 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AM102" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="AM102" t="s" s="2">
+      <c r="AN102" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="AN102" t="s" s="2">
+      <c r="AO102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP102" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>566</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14970,19 +14967,19 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -15031,7 +15028,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15043,19 +15040,19 @@
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM103" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="AK103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM103" t="s" s="2">
+      <c r="AN103" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -15066,10 +15063,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15184,10 +15181,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15304,14 +15301,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -15333,10 +15330,10 @@
         <v>139</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>142</v>
@@ -15391,7 +15388,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15426,10 +15423,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15452,13 +15449,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15509,7 +15506,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15518,7 +15515,7 @@
         <v>93</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>105</v>
@@ -15530,10 +15527,10 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15544,10 +15541,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15570,13 +15567,13 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15627,7 +15624,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15636,7 +15633,7 @@
         <v>93</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>105</v>
@@ -15648,10 +15645,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15662,10 +15659,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15691,16 +15688,16 @@
         <v>191</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="N109" t="s" s="2">
+      <c r="O109" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15728,11 +15725,11 @@
         <v>117</v>
       </c>
       <c r="Y109" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="Z109" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="Z109" t="s" s="2">
-        <v>600</v>
-      </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15749,7 +15746,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15767,10 +15764,10 @@
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AM109" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>498</v>
@@ -15784,10 +15781,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15813,16 +15810,16 @@
         <v>191</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="N110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15850,11 +15847,11 @@
         <v>207</v>
       </c>
       <c r="Y110" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="Z110" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="Z110" t="s" s="2">
-        <v>609</v>
-      </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
       </c>
@@ -15871,7 +15868,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15889,10 +15886,10 @@
         <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AM110" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>498</v>
@@ -15906,10 +15903,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15932,17 +15929,17 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15991,7 +15988,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16015,7 +16012,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -16026,10 +16023,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16055,10 +16052,10 @@
         <v>217</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16109,7 +16106,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16130,10 +16127,10 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16144,10 +16141,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16170,16 +16167,16 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16229,7 +16226,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16250,10 +16247,10 @@
         <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AN113" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -16264,10 +16261,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16290,16 +16287,16 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L114" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="M114" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16349,7 +16346,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16370,10 +16367,10 @@
         <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16384,10 +16381,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16410,19 +16407,19 @@
         <v>94</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="N115" t="s" s="2">
+      <c r="O115" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16471,7 +16468,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16492,10 +16489,10 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AN115" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16506,10 +16503,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16624,10 +16621,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16744,14 +16741,14 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16773,10 +16770,10 @@
         <v>139</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>142</v>
@@ -16831,7 +16828,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16866,10 +16863,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16895,13 +16892,13 @@
         <v>191</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="O119" t="s" s="2">
         <v>206</v>
@@ -16953,7 +16950,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>93</v>
@@ -16971,7 +16968,7 @@
         <v>82</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>212</v>
@@ -16988,10 +16985,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17106,10 +17103,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17226,10 +17223,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17346,10 +17343,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>239</v>
@@ -17470,10 +17467,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="B124" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17588,10 +17585,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="B125" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17708,10 +17705,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="B126" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17830,10 +17827,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="B127" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17950,10 +17947,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="B128" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18070,10 +18067,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="B129" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18190,10 +18187,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="B130" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18312,10 +18309,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C131" t="s" s="2">
         <v>292</v>
@@ -18436,10 +18433,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18554,10 +18551,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18674,10 +18671,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18796,10 +18793,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18916,10 +18913,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19036,10 +19033,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19156,10 +19153,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19278,10 +19275,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C139" t="s" s="2">
         <v>304</v>
@@ -19402,10 +19399,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19520,10 +19517,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19640,10 +19637,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19762,10 +19759,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19882,10 +19879,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20002,10 +19999,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20122,10 +20119,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20244,10 +20241,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C147" t="s" s="2">
         <v>316</v>
@@ -20368,10 +20365,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20486,10 +20483,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20606,10 +20603,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20728,10 +20725,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20848,10 +20845,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20968,10 +20965,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21088,10 +21085,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21210,10 +21207,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C155" t="s" s="2">
         <v>328</v>
@@ -21334,10 +21331,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21452,10 +21449,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21572,10 +21569,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21694,10 +21691,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21814,10 +21811,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21934,10 +21931,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22054,10 +22051,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22176,10 +22173,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>339</v>
@@ -22207,7 +22204,7 @@
         <v>229</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="M163" t="s" s="2">
         <v>231</v>
@@ -22300,10 +22297,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22418,10 +22415,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22538,10 +22535,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22660,10 +22657,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22780,10 +22777,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22900,10 +22897,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23020,10 +23017,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23142,10 +23139,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23264,10 +23261,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23293,13 +23290,13 @@
         <v>413</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="M172" t="s" s="2">
         <v>415</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="O172" t="s" s="2">
         <v>417</v>
@@ -23349,7 +23346,7 @@
         <v>419</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23367,7 +23364,7 @@
         <v>82</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>422</v>
@@ -23384,10 +23381,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C173" t="s" s="2">
         <v>426</v>
@@ -23415,13 +23412,13 @@
         <v>427</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="M173" t="s" s="2">
         <v>415</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="O173" t="s" s="2">
         <v>417</v>
@@ -23473,7 +23470,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23491,7 +23488,7 @@
         <v>82</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>422</v>
@@ -23508,10 +23505,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="B174" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="B174" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23626,10 +23623,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="B175" t="s" s="2">
         <v>715</v>
-      </c>
-      <c r="B175" t="s" s="2">
-        <v>716</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23746,10 +23743,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="B176" t="s" s="2">
         <v>717</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>718</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23868,10 +23865,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="B177" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23990,10 +23987,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="B178" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="B178" t="s" s="2">
-        <v>722</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24110,10 +24107,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="B179" t="s" s="2">
         <v>723</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>724</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24228,10 +24225,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="B180" t="s" s="2">
         <v>725</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>726</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24350,10 +24347,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24379,13 +24376,13 @@
         <v>191</v>
       </c>
       <c r="L181" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="M181" t="s" s="2">
         <v>728</v>
       </c>
-      <c r="M181" t="s" s="2">
+      <c r="N181" t="s" s="2">
         <v>729</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>730</v>
       </c>
       <c r="O181" t="s" s="2">
         <v>483</v>
@@ -24437,7 +24434,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -24472,10 +24469,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24559,7 +24556,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24594,10 +24591,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24623,16 +24620,16 @@
         <v>83</v>
       </c>
       <c r="L183" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="M183" t="s" s="2">
         <v>733</v>
       </c>
-      <c r="M183" t="s" s="2">
-        <v>734</v>
-      </c>
       <c r="N183" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="O183" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="O183" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -24681,7 +24678,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24702,10 +24699,10 @@
         <v>82</v>
       </c>
       <c r="AM183" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AN183" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="AN183" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T12:49:28+00:00</t>
+    <t>2024-11-15T13:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T13:03:47+00:00</t>
+    <t>2024-11-29T07:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T07:41:39+00:00</t>
+    <t>2024-11-29T10:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T10:20:07+00:00</t>
+    <t>2024-12-11T08:38:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T08:38:49+00:00</t>
+    <t>2024-12-11T09:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T09:50:58+00:00</t>
+    <t>2024-12-16T15:09:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:09:03+00:00</t>
+    <t>2024-12-16T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-basic-observation.xlsx
+++ b/StructureDefinition-dk-core-basic-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:16:17+00:00</t>
+    <t>2024-12-16T15:31:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
